--- a/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -120,16 +120,16 @@
     <t xml:space="preserve">prop_overall</t>
   </si>
   <si>
+    <t xml:space="preserve">Baseline Tributaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developed Tributaries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main Stem</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pooled Water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline Tributaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Tributaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Main Stem</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.3</t>
@@ -534,19 +534,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>-8.1725655950318</v>
+        <v>-0.717915947713745</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.014012062790606</v>
+        <v>-0.0297833450290996</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.286631082504031</v>
+        <v>-0.28663108250409</v>
       </c>
       <c r="E2" t="n">
         <v>0.0875999099217127</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000876440420154536</v>
+        <v>0.000876440420154894</v>
       </c>
     </row>
     <row r="3">
@@ -554,19 +554,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>-7.84543894638924</v>
+        <v>-0.022591783789478</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.250024544253643</v>
+        <v>-0.53143975862286</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.21077791749879</v>
+        <v>-5.2107779174987</v>
       </c>
       <c r="E3" t="n">
         <v>0.121001977133052</v>
       </c>
       <c r="F3" t="n">
-        <v>0.415305026002933</v>
+        <v>0.415305026002918</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +574,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>-7.14225801761809</v>
+        <v>1.47205468849941</v>
       </c>
       <c r="C4" t="n">
-        <v>0.187487225486383</v>
+        <v>0.398513538559939</v>
       </c>
       <c r="D4" t="n">
-        <v>3.74468082570236</v>
+        <v>3.74468082570238</v>
       </c>
       <c r="E4" t="n">
         <v>0.04293488120426</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0698965728106095</v>
+        <v>0.0698965728106101</v>
       </c>
     </row>
     <row r="5">
@@ -594,19 +594,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>-8.27408266551836</v>
+        <v>-0.933695592854292</v>
       </c>
       <c r="C5" t="n">
-        <v>0.12760510129126</v>
+        <v>0.271231068260557</v>
       </c>
       <c r="D5" t="n">
-        <v>2.54333047793761</v>
+        <v>2.54333047793763</v>
       </c>
       <c r="E5" t="n">
         <v>0.038922921629668</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0291078611234915</v>
+        <v>0.0291078611234919</v>
       </c>
     </row>
     <row r="6">
@@ -614,19 +614,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>-7.70050455976282</v>
+        <v>0.28547355305504</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.158711220830925</v>
+        <v>-0.337348691669091</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.28813384908956</v>
+        <v>-3.28813384908954</v>
       </c>
       <c r="E6" t="n">
         <v>0.110503944823559</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1492417118833</v>
+        <v>0.149241711883297</v>
       </c>
     </row>
     <row r="7">
@@ -634,19 +634,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>-8.13947261772757</v>
+        <v>-0.647575158079768</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0188178723673924</v>
+        <v>-0.0399983352777558</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.37737288239192</v>
+        <v>-0.377372882392009</v>
       </c>
       <c r="E7" t="n">
         <v>0.0506477221978761</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000844172869165591</v>
+        <v>0.00084417286916599</v>
       </c>
     </row>
     <row r="8">
@@ -654,19 +654,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>-8.12314649366367</v>
+        <v>-0.612873159291364</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0669701423353815</v>
+        <v>-0.142348409768712</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.36941520240538</v>
+        <v>-1.36941520240532</v>
       </c>
       <c r="E8" t="n">
-        <v>0.086896743055911</v>
+        <v>0.0868967430559108</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0198294828253367</v>
+        <v>0.0198294828253351</v>
       </c>
     </row>
     <row r="9">
@@ -674,19 +674,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>-7.6900306591864</v>
+        <v>0.307736356136214</v>
       </c>
       <c r="C9" t="n">
-        <v>0.121425836661347</v>
+        <v>0.258096730137104</v>
       </c>
       <c r="D9" t="n">
-        <v>2.42224089999984</v>
+        <v>2.42224089999978</v>
       </c>
       <c r="E9" t="n">
-        <v>0.040565611178913</v>
+        <v>0.0405656111789131</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0275635340317739</v>
+        <v>0.0275635340317728</v>
       </c>
     </row>
     <row r="10">
@@ -694,19 +694,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>-8.46940607809783</v>
+        <v>-1.34886534166633</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0248002690051709</v>
+        <v>-0.0527142205707595</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.507054159716845</v>
+        <v>-0.507054159716842</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0866613819795708</v>
+        <v>0.0866613819795709</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0027105659581416</v>
+        <v>0.00271056595814157</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +714,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-6.68800304118605</v>
+        <v>2.43759651459862</v>
       </c>
       <c r="C11" t="n">
-        <v>0.104482603187837</v>
+        <v>0.222083034224444</v>
       </c>
       <c r="D11" t="n">
-        <v>2.09588452212561</v>
+        <v>2.09588452212559</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0511861714215746</v>
+        <v>0.0511861714215747</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0263307865521675</v>
+        <v>0.0263307865521671</v>
       </c>
     </row>
     <row r="12">
@@ -734,19 +734,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>-8.03978901993609</v>
+        <v>-0.435692651475856</v>
       </c>
       <c r="C12" t="n">
-        <v>0.221590236825858</v>
+        <v>0.471001206395364</v>
       </c>
       <c r="D12" t="n">
-        <v>4.45725232700327</v>
+        <v>4.45725232700321</v>
       </c>
       <c r="E12" t="n">
         <v>0.0563856427898963</v>
       </c>
       <c r="F12" t="n">
-        <v>0.131906417987017</v>
+        <v>0.131906417987013</v>
       </c>
     </row>
     <row r="13">
@@ -754,19 +754,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>-8.30927912034376</v>
+        <v>-1.00850742987864</v>
       </c>
       <c r="C13" t="n">
-        <v>0.458740591624856</v>
+        <v>0.975076227061556</v>
       </c>
       <c r="D13" t="n">
-        <v>9.64831502542429</v>
+        <v>9.64831502542435</v>
       </c>
       <c r="E13" t="n">
         <v>0.136903951920593</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64065511750568</v>
+        <v>1.6406551175057</v>
       </c>
     </row>
     <row r="14">
@@ -774,16 +774,16 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>-7.43495002131093</v>
+        <v>0.84992309634834</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.0965576032193408</v>
+        <v>-0.205238047733554</v>
       </c>
       <c r="D14" t="n">
         <v>-1.95830293560698</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0718013300339953</v>
+        <v>0.0718013300339954</v>
       </c>
       <c r="F14" t="n">
         <v>0.0329616381772914</v>
@@ -794,19 +794,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>-7.7893524230696</v>
+        <v>0.0966229457242366</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.137012578312792</v>
+        <v>-0.291227134376775</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.77641468110913</v>
+        <v>-2.77641468110915</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0702205328633106</v>
+        <v>0.0702205328633105</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0646860041866481</v>
+        <v>0.0646860041866491</v>
       </c>
     </row>
     <row r="16">
@@ -814,19 +814,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>-7.84658650144635</v>
+        <v>-0.0250309698476938</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0179939849391819</v>
+        <v>-0.0382471210628075</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.373753697627492</v>
+        <v>-0.373753697627491</v>
       </c>
       <c r="E16" t="n">
-        <v>0.115064847518504</v>
+        <v>0.115064847518505</v>
       </c>
       <c r="F16" t="n">
-        <v>0.00201817910606921</v>
+        <v>0.0020181791060692</v>
       </c>
     </row>
     <row r="17">
@@ -834,16 +834,16 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>-8.07428056065102</v>
+        <v>-0.509006158062963</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.149928397787477</v>
+        <v>-0.318680359037307</v>
       </c>
       <c r="D17" t="n">
         <v>-3.0769561207648</v>
       </c>
       <c r="E17" t="n">
-        <v>0.093531052099304</v>
+        <v>0.0935310520993041</v>
       </c>
       <c r="F17" t="n">
         <v>0.108543290895616</v>
@@ -854,19 +854,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>-7.32979120041937</v>
+        <v>1.07344346535252</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.190707227742674</v>
+        <v>-0.40535781549665</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.77781073357642</v>
+        <v>-3.77781073357638</v>
       </c>
       <c r="E18" t="n">
-        <v>0.027069874053581</v>
+        <v>0.0270698740535809</v>
       </c>
       <c r="F18" t="n">
-        <v>0.044120707395963</v>
+        <v>0.0441207073959621</v>
       </c>
     </row>
     <row r="19">
@@ -874,19 +874,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>-6.32330375515454</v>
+        <v>3.21278321123707</v>
       </c>
       <c r="C19" t="n">
-        <v>0.154630507165484</v>
+        <v>0.328674929291705</v>
       </c>
       <c r="D19" t="n">
-        <v>3.09981185028872</v>
+        <v>3.09981185028873</v>
       </c>
       <c r="E19" t="n">
         <v>0.0499478834912942</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0561303589051862</v>
+        <v>0.0561303589051866</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +894,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>-7.19927136885919</v>
+        <v>1.35086993956888</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.153882099082141</v>
+        <v>-0.327084150224992</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.06847805809597</v>
+        <v>-3.06847805809598</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0398084117347628</v>
+        <v>0.0398084117347627</v>
       </c>
       <c r="F20" t="n">
-        <v>0.043373102474308</v>
+        <v>0.0433731024743081</v>
       </c>
     </row>
     <row r="21">
@@ -914,19 +914,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>-10.0835063085869</v>
+        <v>-4.77971665846353</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0209899139294039</v>
+        <v>0.0446151189894359</v>
       </c>
       <c r="D21" t="n">
-        <v>0.426521270950441</v>
+        <v>0.426521270950385</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0753706737186193</v>
+        <v>0.0753706737186191</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00164768282001196</v>
+        <v>0.00164768282001153</v>
       </c>
     </row>
     <row r="22">
@@ -934,19 +934,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>-7.69537060961742</v>
+        <v>0.296386022605598</v>
       </c>
       <c r="C22" t="n">
-        <v>0.119284424242269</v>
+        <v>0.253545050211019</v>
       </c>
       <c r="D22" t="n">
-        <v>2.39500675296158</v>
+        <v>2.39500675296149</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0529307621568677</v>
+        <v>0.0529307621568678</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0356202851921313</v>
+        <v>0.0356202851921288</v>
       </c>
     </row>
     <row r="23">
@@ -954,19 +954,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>-6.37482457485504</v>
+        <v>3.10327311466867</v>
       </c>
       <c r="C23" t="n">
-        <v>0.130284489442725</v>
+        <v>0.276926242695213</v>
       </c>
       <c r="D23" t="n">
-        <v>2.5898172776393</v>
+        <v>2.58981727763926</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0337824521174471</v>
+        <v>0.0337824521174472</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0260562545062462</v>
+        <v>0.0260562545062453</v>
       </c>
     </row>
     <row r="24">
@@ -974,19 +974,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>-7.51525956199997</v>
+        <v>0.679221123682808</v>
       </c>
       <c r="C24" t="n">
-        <v>0.116576282112978</v>
+        <v>0.247788757748615</v>
       </c>
       <c r="D24" t="n">
-        <v>2.33671699570136</v>
+        <v>2.33671699570141</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0497543197296459</v>
+        <v>0.0497543197296458</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0317661523106882</v>
+        <v>0.0317661523106895</v>
       </c>
     </row>
     <row r="25">
@@ -994,19 +994,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>-7.60341194381116</v>
+        <v>0.491848797291362</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.190294218436533</v>
+        <v>-0.404479943419665</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.95947804365952</v>
+        <v>-3.95947804365961</v>
       </c>
       <c r="E25" t="n">
         <v>0.118133090394652</v>
       </c>
       <c r="F25" t="n">
-        <v>0.233346820206744</v>
+        <v>0.233346820206754</v>
       </c>
     </row>
   </sheetData>
@@ -1042,16 +1042,16 @@
         <v>35</v>
       </c>
       <c r="B2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.416666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0492227979274611</v>
+        <v>0.282383419689119</v>
       </c>
     </row>
     <row r="3">
@@ -1059,16 +1059,16 @@
         <v>36</v>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.25</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D3" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E3" t="n">
-        <v>0.282383419689119</v>
+        <v>0.326424870466321</v>
       </c>
     </row>
     <row r="4">
@@ -1076,16 +1076,16 @@
         <v>37</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E4" t="n">
-        <v>0.326424870466321</v>
+        <v>0.341968911917098</v>
       </c>
     </row>
     <row r="5">
@@ -1093,16 +1093,16 @@
         <v>38</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>0.291666666666667</v>
+        <v>0.416666666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>132</v>
+        <v>19</v>
       </c>
       <c r="E5" t="n">
-        <v>0.341968911917098</v>
+        <v>0.0492227979274611</v>
       </c>
     </row>
     <row r="6">

--- a/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t xml:space="preserve">Sample_ID</t>
   </si>
@@ -33,6 +33,12 @@
     <t xml:space="preserve">Cooks_D</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaDE_64</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_65</t>
   </si>
   <si>
@@ -48,10 +54,10 @@
     <t xml:space="preserve">WaDE_187</t>
   </si>
   <si>
-    <t xml:space="preserve">WaDE_195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaDE_305</t>
+    <t xml:space="preserve">WaDE_193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaDE_338</t>
   </si>
   <si>
     <t xml:space="preserve">WaDE_358</t>
@@ -60,9 +66,6 @@
     <t xml:space="preserve">WaDE_390</t>
   </si>
   <si>
-    <t xml:space="preserve">WaDE_393</t>
-  </si>
-  <si>
     <t xml:space="preserve">WaDE_397</t>
   </si>
   <si>
@@ -84,6 +87,12 @@
     <t xml:space="preserve">WaDE_464</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_480</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaDE_481</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_520</t>
   </si>
   <si>
@@ -120,16 +129,16 @@
     <t xml:space="preserve">prop_overall</t>
   </si>
   <si>
-    <t xml:space="preserve">Baseline Tributaries</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developed Tributaries</t>
-  </si>
-  <si>
     <t xml:space="preserve">Main Stem</t>
   </si>
   <si>
-    <t xml:space="preserve">Pooled Water</t>
+    <t xml:space="preserve">Non-Perennial Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Developed Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perennial Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.3</t>
@@ -141,6 +150,9 @@
     <t xml:space="preserve">EFK10.0</t>
   </si>
   <si>
+    <t xml:space="preserve">EFK13.8</t>
+  </si>
+  <si>
     <t xml:space="preserve">EFK23.5</t>
   </si>
   <si>
@@ -168,10 +180,10 @@
     <t xml:space="preserve">NBO5</t>
   </si>
   <si>
-    <t xml:space="preserve">Pinhook Branch</t>
-  </si>
-  <si>
     <t xml:space="preserve">WBK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WBK3</t>
   </si>
   <si>
     <t xml:space="preserve">High</t>
@@ -534,19 +546,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.717915947713745</v>
+        <v>-0.387305226434427</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0297833450290996</v>
+        <v>-0.0416806888032145</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.28663108250409</v>
+        <v>-0.40389732236509</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0875999099217127</v>
+        <v>0.101000612644682</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000876440420154894</v>
+        <v>0.00152730338517872</v>
       </c>
     </row>
     <row r="3">
@@ -554,19 +566,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.022591783789478</v>
+        <v>-2.33791297965946</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.53143975862286</v>
+        <v>0.172069073591965</v>
       </c>
       <c r="D3" t="n">
-        <v>-5.2107779174987</v>
+        <v>1.76609283692154</v>
       </c>
       <c r="E3" t="n">
-        <v>0.121001977133052</v>
+        <v>0.198672306697932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.415305026002918</v>
+        <v>0.0644425911407853</v>
       </c>
     </row>
     <row r="4">
@@ -574,19 +586,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>1.47205468849941</v>
+        <v>-0.727436396024039</v>
       </c>
       <c r="C4" t="n">
-        <v>0.398513538559939</v>
+        <v>-0.0202628967188053</v>
       </c>
       <c r="D4" t="n">
-        <v>3.74468082570238</v>
+        <v>-0.207748871312318</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04293488120426</v>
+        <v>0.196922820998556</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0698965728106101</v>
+        <v>0.000881931518498863</v>
       </c>
     </row>
     <row r="5">
@@ -594,19 +606,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.933695592854292</v>
+        <v>-0.0315692541585324</v>
       </c>
       <c r="C5" t="n">
-        <v>0.271231068260557</v>
+        <v>-0.522462288253806</v>
       </c>
       <c r="D5" t="n">
-        <v>2.54333047793763</v>
+        <v>-5.29580916818599</v>
       </c>
       <c r="E5" t="n">
-        <v>0.038922921629668</v>
+        <v>0.17836901052879</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0291078611234919</v>
+        <v>0.507371420241314</v>
       </c>
     </row>
     <row r="6">
@@ -614,19 +626,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.28547355305504</v>
+        <v>1.44200034819106</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.337348691669091</v>
+        <v>0.428567878868292</v>
       </c>
       <c r="D6" t="n">
-        <v>-3.28813384908954</v>
+        <v>4.08971404105237</v>
       </c>
       <c r="E6" t="n">
-        <v>0.110503944823559</v>
+        <v>0.0729889325617565</v>
       </c>
       <c r="F6" t="n">
-        <v>0.149241711883297</v>
+        <v>0.109742975749179</v>
       </c>
     </row>
     <row r="7">
@@ -634,19 +646,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.647575158079768</v>
+        <v>-0.934383996712214</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0399983352777558</v>
+        <v>0.271919472118479</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.377372882392009</v>
+        <v>2.55253550609284</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0506477221978761</v>
+        <v>0.0419931768601787</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00084417286916599</v>
+        <v>0.0237997539148055</v>
       </c>
     </row>
     <row r="8">
@@ -654,19 +666,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.612873159291364</v>
+        <v>0.321836149856817</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.142348409768712</v>
+        <v>-0.373711288470867</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.36941520240532</v>
+        <v>-3.80221576646068</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0868967430559108</v>
+        <v>0.184487756978997</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0198294828253351</v>
+        <v>0.272539425468178</v>
       </c>
     </row>
     <row r="9">
@@ -674,19 +686,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>0.307736356136214</v>
+        <v>-0.0869103623672581</v>
       </c>
       <c r="C9" t="n">
-        <v>0.258096730137104</v>
+        <v>-0.0899219545421078</v>
       </c>
       <c r="D9" t="n">
-        <v>2.42224089999978</v>
+        <v>-0.87647247125342</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0405656111789131</v>
+        <v>0.111440559882582</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0275635340317728</v>
+        <v>0.00802882726089831</v>
       </c>
     </row>
     <row r="10">
@@ -694,19 +706,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>-1.34886534166633</v>
+        <v>1.26907940787703</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.0527142205707595</v>
+        <v>0.0938908185343434</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.507054159716842</v>
+        <v>0.911870327984426</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0866613819795709</v>
+        <v>0.10502346002262</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00271056595814157</v>
+        <v>0.00813129267127537</v>
       </c>
     </row>
     <row r="11">
@@ -714,19 +726,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>2.43759651459862</v>
+        <v>0.313999146718332</v>
       </c>
       <c r="C11" t="n">
-        <v>0.222083034224444</v>
+        <v>0.251833939554986</v>
       </c>
       <c r="D11" t="n">
-        <v>2.09588452212559</v>
+        <v>2.36480297066738</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0511861714215747</v>
+        <v>0.0426512747890243</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0263307865521671</v>
+        <v>0.0207620642827134</v>
       </c>
     </row>
     <row r="12">
@@ -734,19 +746,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>-0.435692651475856</v>
+        <v>-1.35732107164424</v>
       </c>
       <c r="C12" t="n">
-        <v>0.471001206395364</v>
+        <v>-0.0442584905928508</v>
       </c>
       <c r="D12" t="n">
-        <v>4.45725232700321</v>
+        <v>-0.435646026482906</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0563856427898963</v>
+        <v>0.128720989730283</v>
       </c>
       <c r="F12" t="n">
-        <v>0.131906417987013</v>
+        <v>0.00233656779782857</v>
       </c>
     </row>
     <row r="13">
@@ -754,19 +766,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>-1.00850742987864</v>
+        <v>-0.422673911002417</v>
       </c>
       <c r="C13" t="n">
-        <v>0.975076227061556</v>
+        <v>0.457982465921924</v>
       </c>
       <c r="D13" t="n">
-        <v>9.64831502542435</v>
+        <v>4.38656082882528</v>
       </c>
       <c r="E13" t="n">
-        <v>0.136903951920593</v>
+        <v>0.0798026905623162</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6406551175057</v>
+        <v>0.139060453397935</v>
       </c>
     </row>
     <row r="14">
@@ -774,19 +786,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>0.84992309634834</v>
+        <v>-1.00176185852295</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.205238047733554</v>
+        <v>0.968330655705868</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.95830293560698</v>
+        <v>9.58681384207902</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0718013300339954</v>
+        <v>0.138747803097319</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0329616381772914</v>
+        <v>1.23385212983561</v>
       </c>
     </row>
     <row r="15">
@@ -794,19 +806,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0966229457242366</v>
+        <v>0.861069521764568</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.291227134376775</v>
+        <v>-0.216384473149781</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.77641468110915</v>
+        <v>-2.07723339585864</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0702205328633105</v>
+        <v>0.0839626841828931</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0646860041866491</v>
+        <v>0.0329581248648581</v>
       </c>
     </row>
     <row r="16">
@@ -814,19 +826,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.0250309698476938</v>
+        <v>0.112377057693675</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.0382471210628075</v>
+        <v>-0.306981246346213</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.373753697627491</v>
+        <v>-3.2150102790222</v>
       </c>
       <c r="E16" t="n">
-        <v>0.115064847518505</v>
+        <v>0.230354866792812</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0020181791060692</v>
+        <v>0.257804414810681</v>
       </c>
     </row>
     <row r="17">
@@ -834,19 +846,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.509006158062963</v>
+        <v>-0.038710790838215</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.318680359037307</v>
+        <v>-0.0245673000722863</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.0769561207648</v>
+        <v>-0.243917120369347</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0935310520993041</v>
+        <v>0.143629178260818</v>
       </c>
       <c r="F17" t="n">
-        <v>0.108543290895616</v>
+        <v>0.000831541898203975</v>
       </c>
     </row>
     <row r="18">
@@ -854,19 +866,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>1.07344346535252</v>
+        <v>-0.517877312019397</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.40535781549665</v>
+        <v>-0.309809205080874</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.77781073357638</v>
+        <v>-3.06010250198727</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0270698740535809</v>
+        <v>0.134736755007249</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0441207073959621</v>
+        <v>0.12151461900064</v>
       </c>
     </row>
     <row r="19">
@@ -874,19 +886,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>3.21278321123707</v>
+        <v>1.08126691866913</v>
       </c>
       <c r="C19" t="n">
-        <v>0.328674929291705</v>
+        <v>-0.413181268813259</v>
       </c>
       <c r="D19" t="n">
-        <v>3.09981185028873</v>
+        <v>-3.85564647868082</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0499478834912942</v>
+        <v>0.0305656475135389</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0561303589051866</v>
+        <v>0.0390596514136744</v>
       </c>
     </row>
     <row r="20">
@@ -894,19 +906,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>1.35086993956888</v>
+        <v>0.304642524117584</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.327084150224992</v>
+        <v>0.0909783829797238</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.06847805809598</v>
+        <v>0.883472330557628</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0398084117347627</v>
+        <v>0.104795840635681</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0433731024743081</v>
+        <v>0.00761424090359632</v>
       </c>
     </row>
     <row r="21">
@@ -914,19 +926,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>-4.77971665846353</v>
+        <v>-1.15371840774757</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0446151189894359</v>
+        <v>-0.0792700253514053</v>
       </c>
       <c r="D21" t="n">
-        <v>0.426521270950385</v>
+        <v>-0.799953021861128</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0753706737186191</v>
+        <v>0.171064772012977</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00164768282001153</v>
+        <v>0.0110049407041009</v>
       </c>
     </row>
     <row r="22">
@@ -934,19 +946,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>0.296386022605598</v>
+        <v>3.21648403901593</v>
       </c>
       <c r="C22" t="n">
-        <v>0.253545050211019</v>
+        <v>0.324974101512846</v>
       </c>
       <c r="D22" t="n">
-        <v>2.39500675296149</v>
+        <v>3.06858557009487</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0529307621568678</v>
+        <v>0.0532123255139728</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0356202851921288</v>
+        <v>0.0441016536718979</v>
       </c>
     </row>
     <row r="23">
@@ -954,19 +966,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>3.10327311466867</v>
+        <v>1.35985235890837</v>
       </c>
       <c r="C23" t="n">
-        <v>0.276926242695213</v>
+        <v>-0.336066569564482</v>
       </c>
       <c r="D23" t="n">
-        <v>2.58981727763926</v>
+        <v>-3.15904759084562</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0337824521174472</v>
+        <v>0.04463383199951</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0260562545062453</v>
+        <v>0.0388530760163527</v>
       </c>
     </row>
     <row r="24">
@@ -974,19 +986,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>0.679221123682808</v>
+        <v>-4.77585579013447</v>
       </c>
       <c r="C24" t="n">
-        <v>0.247788757748615</v>
+        <v>0.0407542506603729</v>
       </c>
       <c r="D24" t="n">
-        <v>2.33671699570141</v>
+        <v>0.389960753540153</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0497543197296458</v>
+        <v>0.0779900841321501</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0317661523106895</v>
+        <v>0.00107192488401761</v>
       </c>
     </row>
     <row r="25">
@@ -994,19 +1006,79 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>0.491848797291362</v>
+        <v>0.302361818813422</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.404479943419665</v>
+        <v>0.247569254003195</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.95947804365961</v>
+        <v>2.34156231843771</v>
       </c>
       <c r="E25" t="n">
-        <v>0.118133090394652</v>
+        <v>0.0563443513707369</v>
       </c>
       <c r="F25" t="n">
-        <v>0.233346820206754</v>
+        <v>0.0272814239790748</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="n">
+        <v>3.09990777382625</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.280291583537634</v>
+      </c>
+      <c r="D26" t="n">
+        <v>2.62129107939092</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0347913966566757</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.0206395361134537</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" t="n">
+        <v>0.695762194658104</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.231247686773319</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.21233268186614</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0776717875718957</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0343476818214027</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28" t="n">
+        <v>0.492276868895541</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.404908015023845</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-3.96920230798655</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.121507929509856</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.181590029489928</v>
       </c>
     </row>
   </sheetData>
@@ -1022,98 +1094,98 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.296296296296296</v>
       </c>
       <c r="D2" t="n">
-        <v>109</v>
+        <v>132</v>
       </c>
       <c r="E2" t="n">
-        <v>0.282383419689119</v>
+        <v>0.341968911917098</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.407407407407407</v>
       </c>
       <c r="D3" t="n">
-        <v>126</v>
+        <v>19</v>
       </c>
       <c r="E3" t="n">
-        <v>0.326424870466321</v>
+        <v>0.0492227979274611</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.291666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D4" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E4" t="n">
-        <v>0.341968911917098</v>
+        <v>0.326424870466321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
-        <v>0.416666666666667</v>
+        <v>0.259259259259259</v>
       </c>
       <c r="D5" t="n">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0492227979274611</v>
+        <v>0.282383419689119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D6" t="n">
         <v>4</v>
@@ -1124,13 +1196,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
@@ -1141,13 +1213,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
@@ -1158,13 +1230,13 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.25</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
@@ -1175,13 +1247,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.222222222222222</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -1192,115 +1264,115 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.208333333333333</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0129533678756477</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.185185185185185</v>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0103626943005181</v>
+        <v>0.0129533678756477</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0103626943005181</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.00518134715025907</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.0740740740740741</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.00518134715025907</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0833333333333333</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0155440414507772</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -1311,30 +1383,30 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B18" t="n">
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0259067357512953</v>
+        <v>0.0155440414507772</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D19" t="n">
         <v>5</v>
@@ -1345,52 +1417,69 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.291666666666667</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D20" t="n">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0.339378238341969</v>
+        <v>0.0207253886010363</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B21" t="n">
         <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>0.291666666666667</v>
+        <v>0.259259259259259</v>
       </c>
       <c r="D21" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E21" t="n">
-        <v>0.284974093264249</v>
+        <v>0.339378238341969</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>0.416666666666667</v>
+        <v>0.259259259259259</v>
       </c>
       <c r="D22" t="n">
+        <v>110</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.284974093264249</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" t="n">
+        <v>13</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.481481481481481</v>
+      </c>
+      <c r="D23" t="n">
         <v>145</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E23" t="n">
         <v>0.375647668393782</v>
       </c>
     </row>

--- a/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -132,13 +132,13 @@
     <t xml:space="preserve">Main Stem</t>
   </si>
   <si>
-    <t xml:space="preserve">Non-Perennial Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Developed Tribs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perennial Tribs</t>
+    <t xml:space="preserve">NP Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P Tribs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PD Tribs</t>
   </si>
   <si>
     <t xml:space="preserve">BSL4.3</t>
@@ -1148,16 +1148,16 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>0.037037037037037</v>
+        <v>0.259259259259259</v>
       </c>
       <c r="D4" t="n">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E4" t="n">
-        <v>0.326424870466321</v>
+        <v>0.282383419689119</v>
       </c>
     </row>
     <row r="5">
@@ -1165,16 +1165,16 @@
         <v>41</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.259259259259259</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D5" t="n">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="E5" t="n">
-        <v>0.282383419689119</v>
+        <v>0.326424870466321</v>
       </c>
     </row>
     <row r="6">

--- a/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -1120,10 +1120,10 @@
         <v>0.296296296296296</v>
       </c>
       <c r="D2" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>0.341968911917098</v>
+        <v>0.329015544041451</v>
       </c>
     </row>
     <row r="3">
@@ -1131,16 +1131,16 @@
         <v>39</v>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.407407407407407</v>
+        <v>0.296296296296296</v>
       </c>
       <c r="D3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0492227979274611</v>
+        <v>0.0362694300518135</v>
       </c>
     </row>
     <row r="4">
@@ -1148,16 +1148,16 @@
         <v>40</v>
       </c>
       <c r="B4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>0.259259259259259</v>
+        <v>0.185185185185185</v>
       </c>
       <c r="D4" t="n">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="E4" t="n">
-        <v>0.282383419689119</v>
+        <v>0.253886010362694</v>
       </c>
     </row>
     <row r="5">
@@ -1171,32 +1171,30 @@
         <v>0.037037037037037</v>
       </c>
       <c r="D5" t="n">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.326424870466321</v>
+        <v>0.303108808290155</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s">
-        <v>42</v>
-      </c>
+      <c r="A6"/>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.037037037037037</v>
+        <v>0.185185185185185</v>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0103626943005181</v>
+        <v>0.077720207253886</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -1205,15 +1203,15 @@
         <v>0.037037037037037</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00259067357512953</v>
+        <v>0.0103626943005181</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
@@ -1222,15 +1220,15 @@
         <v>0.037037037037037</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.00259067357512953</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
@@ -1247,13 +1245,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>0.222222222222222</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
@@ -1264,13 +1262,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0.037037037037037</v>
+        <v>0.222222222222222</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
@@ -1281,41 +1279,41 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C12" t="n">
-        <v>0.185185185185185</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0129533678756477</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>0.037037037037037</v>
+        <v>0.185185185185185</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0103626943005181</v>
+        <v>0.0129533678756477</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
@@ -1324,72 +1322,72 @@
         <v>0.037037037037037</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0103626943005181</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0740740740740741</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.00518134715025907</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0740740740740741</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.00518134715025907</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.111111111111111</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0155440414507772</v>
+        <v>0.0284974093264249</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>0.037037037037037</v>
+        <v>0.111111111111111</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -1400,7 +1398,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -1409,15 +1407,15 @@
         <v>0.037037037037037</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0129533678756477</v>
+        <v>0.0155440414507772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
@@ -1426,32 +1424,32 @@
         <v>0.037037037037037</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0207253886010363</v>
+        <v>0.0129533678756477</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C21" t="n">
-        <v>0.259259259259259</v>
+        <v>0.037037037037037</v>
       </c>
       <c r="D21" t="n">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0.339378238341969</v>
+        <v>0.0207253886010363</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
@@ -1460,26 +1458,43 @@
         <v>0.259259259259259</v>
       </c>
       <c r="D22" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="E22" t="n">
-        <v>0.284974093264249</v>
+        <v>0.339378238341969</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>58</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.259259259259259</v>
+      </c>
+      <c r="D23" t="n">
+        <v>110</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.284974093264249</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
         <v>59</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B24" t="n">
         <v>13</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C24" t="n">
         <v>0.481481481481481</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D24" t="n">
         <v>145</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E24" t="n">
         <v>0.375647668393782</v>
       </c>
     </row>

--- a/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
+++ b/Copper/5. Statistical data analysis/Multiple linear regression/MLR_flagged_obs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve">Sample_ID</t>
   </si>
@@ -39,9 +39,6 @@
     <t xml:space="preserve">WaDE_64</t>
   </si>
   <si>
-    <t xml:space="preserve">WaDE_65</t>
-  </si>
-  <si>
     <t xml:space="preserve">WaDE_67</t>
   </si>
   <si>
@@ -54,13 +51,7 @@
     <t xml:space="preserve">WaDE_187</t>
   </si>
   <si>
-    <t xml:space="preserve">WaDE_193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaDE_338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaDE_358</t>
+    <t xml:space="preserve">WaDE_305</t>
   </si>
   <si>
     <t xml:space="preserve">WaDE_390</t>
@@ -72,16 +63,13 @@
     <t xml:space="preserve">WaDE_398</t>
   </si>
   <si>
-    <t xml:space="preserve">WaDE_420</t>
-  </si>
-  <si>
     <t xml:space="preserve">WaDE_422</t>
   </si>
   <si>
     <t xml:space="preserve">WaDE_425</t>
   </si>
   <si>
-    <t xml:space="preserve">WaDE_442</t>
+    <t xml:space="preserve">WaDE_438</t>
   </si>
   <si>
     <t xml:space="preserve">WaDE_464</t>
@@ -108,6 +96,9 @@
     <t xml:space="preserve">WaDE_626</t>
   </si>
   <si>
+    <t xml:space="preserve">WaDE_634</t>
+  </si>
+  <si>
     <t xml:space="preserve">WaDE_696</t>
   </si>
   <si>
@@ -141,7 +132,7 @@
     <t xml:space="preserve">PD Tribs</t>
   </si>
   <si>
-    <t xml:space="preserve">BSL4.3</t>
+    <t xml:space="preserve">BSL3.2</t>
   </si>
   <si>
     <t xml:space="preserve">BSL5.1</t>
@@ -168,9 +159,6 @@
     <t xml:space="preserve">MCA4</t>
   </si>
   <si>
-    <t xml:space="preserve">MTN2</t>
-  </si>
-  <si>
     <t xml:space="preserve">MTN4</t>
   </si>
   <si>
@@ -178,6 +166,9 @@
   </si>
   <si>
     <t xml:space="preserve">NBO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinhook Branch</t>
   </si>
   <si>
     <t xml:space="preserve">WBK2</t>
@@ -546,19 +537,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.387305226434427</v>
+        <v>-0.383718104928997</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.0416806888032145</v>
+        <v>-0.0169745870278263</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.40389732236509</v>
+        <v>-0.166190984699787</v>
       </c>
       <c r="E2" t="n">
-        <v>0.101000612644682</v>
+        <v>0.110531946097064</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00152730338517872</v>
+        <v>0.000286016533067619</v>
       </c>
     </row>
     <row r="3">
@@ -566,19 +557,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>-2.33791297965946</v>
+        <v>-2.25464773740738</v>
       </c>
       <c r="C3" t="n">
-        <v>0.172069073591965</v>
+        <v>0.131908164804715</v>
       </c>
       <c r="D3" t="n">
-        <v>1.76609283692154</v>
+        <v>1.38085532261565</v>
       </c>
       <c r="E3" t="n">
-        <v>0.198672306697932</v>
+        <v>0.221974480692342</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0644425911407853</v>
+        <v>0.0453340288919641</v>
       </c>
     </row>
     <row r="4">
@@ -586,19 +577,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.727436396024039</v>
+        <v>0.0613529001142289</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0202628967188053</v>
+        <v>-0.586024888796229</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.207748871312318</v>
+        <v>-6.09732410447822</v>
       </c>
       <c r="E4" t="n">
-        <v>0.196922820998556</v>
+        <v>0.212409619068512</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000881931518498863</v>
+        <v>0.835547399712403</v>
       </c>
     </row>
     <row r="5">
@@ -606,19 +597,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0315692541585324</v>
+        <v>1.47407761960364</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.522462288253806</v>
+        <v>0.405174311734126</v>
       </c>
       <c r="D5" t="n">
-        <v>-5.29580916818599</v>
+        <v>3.90832537996883</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17836901052879</v>
+        <v>0.0836756600496279</v>
       </c>
       <c r="F5" t="n">
-        <v>0.507371420241314</v>
+        <v>0.116238528609404</v>
       </c>
     </row>
     <row r="6">
@@ -626,19 +617,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>1.44200034819106</v>
+        <v>-0.912448151767216</v>
       </c>
       <c r="C6" t="n">
-        <v>0.428567878868292</v>
+        <v>0.280267846509843</v>
       </c>
       <c r="D6" t="n">
-        <v>4.08971404105237</v>
+        <v>2.65046743454674</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0729889325617565</v>
+        <v>0.0466586062358</v>
       </c>
       <c r="F6" t="n">
-        <v>0.109742975749179</v>
+        <v>0.0286514766907551</v>
       </c>
     </row>
     <row r="7">
@@ -646,19 +637,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>-0.934383996712214</v>
+        <v>0.369256823533672</v>
       </c>
       <c r="C7" t="n">
-        <v>0.271919472118479</v>
+        <v>-0.396054562666913</v>
       </c>
       <c r="D7" t="n">
-        <v>2.55253550609284</v>
+        <v>-4.08706166331464</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0419931768601787</v>
+        <v>0.199365124870856</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0237997539148055</v>
+        <v>0.346621757190061</v>
       </c>
     </row>
     <row r="8">
@@ -666,19 +657,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>0.321836149856817</v>
+        <v>-0.558691945435835</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.373711288470867</v>
+        <v>-0.16545441572509</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.80221576646068</v>
+        <v>-1.61562644251413</v>
       </c>
       <c r="E8" t="n">
-        <v>0.184487756978997</v>
+        <v>0.105826773706024</v>
       </c>
       <c r="F8" t="n">
-        <v>0.272539425468178</v>
+        <v>0.0257439126573754</v>
       </c>
     </row>
     <row r="9">
@@ -686,19 +677,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0869103623672581</v>
+        <v>-1.2954766876437</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.0899219545421078</v>
+        <v>-0.0695158289355932</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.87647247125342</v>
+        <v>-0.691121566460795</v>
       </c>
       <c r="E9" t="n">
-        <v>0.111440559882582</v>
+        <v>0.137408124496878</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00802882726089831</v>
+        <v>0.00634066331740676</v>
       </c>
     </row>
     <row r="10">
@@ -706,19 +697,19 @@
         <v>14</v>
       </c>
       <c r="B10" t="n">
-        <v>1.26907940787703</v>
+        <v>-0.384990553356305</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0938908185343434</v>
+        <v>0.444633046116124</v>
       </c>
       <c r="D10" t="n">
-        <v>0.911870327984426</v>
+        <v>4.30052790423271</v>
       </c>
       <c r="E10" t="n">
-        <v>0.10502346002262</v>
+        <v>0.0886047159376899</v>
       </c>
       <c r="F10" t="n">
-        <v>0.00813129267127537</v>
+        <v>0.149834683365543</v>
       </c>
     </row>
     <row r="11">
@@ -726,19 +717,19 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.313999146718332</v>
+        <v>-0.915259642788134</v>
       </c>
       <c r="C11" t="n">
-        <v>0.251833939554986</v>
+        <v>0.906748558219452</v>
       </c>
       <c r="D11" t="n">
-        <v>2.36480297066738</v>
+        <v>9.15787908887873</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0426512747890243</v>
+        <v>0.16414531845253</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0207620642827134</v>
+        <v>1.37248082639453</v>
       </c>
     </row>
     <row r="12">
@@ -746,19 +737,19 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>-1.35732107164424</v>
+        <v>0.158252005048466</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.0442584905928508</v>
+        <v>-0.326561667835805</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.435646026482906</v>
+        <v>-3.53749887986263</v>
       </c>
       <c r="E12" t="n">
-        <v>0.128720989730283</v>
+        <v>0.273418005783027</v>
       </c>
       <c r="F12" t="n">
-        <v>0.00233656779782857</v>
+        <v>0.392422460212539</v>
       </c>
     </row>
     <row r="13">
@@ -766,19 +757,19 @@
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.422673911002417</v>
+        <v>0.00593068013098325</v>
       </c>
       <c r="C13" t="n">
-        <v>0.457982465921924</v>
+        <v>-0.0440341325326278</v>
       </c>
       <c r="D13" t="n">
-        <v>4.38656082882528</v>
+        <v>-0.443143377840977</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0798026905623162</v>
+        <v>0.158145175186371</v>
       </c>
       <c r="F13" t="n">
-        <v>0.139060453397935</v>
+        <v>0.00307415685381151</v>
       </c>
     </row>
     <row r="14">
@@ -786,19 +777,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>-1.00176185852295</v>
+        <v>0.0376867111703264</v>
       </c>
       <c r="C14" t="n">
-        <v>0.968330655705868</v>
+        <v>-0.109217722756974</v>
       </c>
       <c r="D14" t="n">
-        <v>9.58681384207902</v>
+        <v>-1.0633626464604</v>
       </c>
       <c r="E14" t="n">
-        <v>0.138747803097319</v>
+        <v>0.100563980790918</v>
       </c>
       <c r="F14" t="n">
-        <v>1.23385212983561</v>
+        <v>0.0105354656572021</v>
       </c>
     </row>
     <row r="15">
@@ -806,19 +797,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>0.861069521764568</v>
+        <v>1.08488956295673</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.216384473149781</v>
+        <v>-0.397866001489802</v>
       </c>
       <c r="D15" t="n">
-        <v>-2.07723339585864</v>
+        <v>-3.73868668994935</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0839626841828931</v>
+        <v>0.0344331272726355</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0329581248648581</v>
+        <v>0.0415385189915636</v>
       </c>
     </row>
     <row r="16">
@@ -826,19 +817,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>0.112377057693675</v>
+        <v>0.328287416061199</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.306981246346213</v>
+        <v>0.0885948541599263</v>
       </c>
       <c r="D16" t="n">
-        <v>-3.2150102790222</v>
+        <v>0.886251834844595</v>
       </c>
       <c r="E16" t="n">
-        <v>0.230354866792812</v>
+        <v>0.147980483639868</v>
       </c>
       <c r="F16" t="n">
-        <v>0.257804414810681</v>
+        <v>0.0113681016473605</v>
       </c>
     </row>
     <row r="17">
@@ -846,19 +837,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>-0.038710790838215</v>
+        <v>-1.14340727080577</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.0245673000722863</v>
+        <v>-0.0544317826984383</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.243917120369347</v>
+        <v>-0.559904435844989</v>
       </c>
       <c r="E17" t="n">
-        <v>0.143629178260818</v>
+        <v>0.194205790388531</v>
       </c>
       <c r="F17" t="n">
-        <v>0.000831541898203975</v>
+        <v>0.00629628825692536</v>
       </c>
     </row>
     <row r="18">
@@ -866,19 +857,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>-0.517877312019397</v>
+        <v>3.20407411404968</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.309809205080874</v>
+        <v>0.331819165391539</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.06010250198727</v>
+        <v>3.16234784126156</v>
       </c>
       <c r="E18" t="n">
-        <v>0.134736755007249</v>
+        <v>0.0612920433110385</v>
       </c>
       <c r="F18" t="n">
-        <v>0.12151461900064</v>
+        <v>0.054414122659124</v>
       </c>
     </row>
     <row r="19">
@@ -886,19 +877,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>1.08126691866913</v>
+        <v>1.36436008211379</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.413181268813259</v>
+        <v>-0.324669625089124</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.85564647868082</v>
+        <v>-3.07524503926507</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0305656475135389</v>
+        <v>0.0496781644233931</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0390596514136744</v>
+        <v>0.0411977065243649</v>
       </c>
     </row>
     <row r="20">
@@ -906,19 +897,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>0.304642524117584</v>
+        <v>-4.72555368140716</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0909783829797238</v>
+        <v>0.055465899254299</v>
       </c>
       <c r="D20" t="n">
-        <v>0.883472330557628</v>
+        <v>0.535469350966676</v>
       </c>
       <c r="E20" t="n">
-        <v>0.104795840635681</v>
+        <v>0.0851924850076341</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00761424090359632</v>
+        <v>0.00222515133197627</v>
       </c>
     </row>
     <row r="21">
@@ -926,19 +917,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>-1.15371840774757</v>
+        <v>0.3227222358448</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0792700253514053</v>
+        <v>0.24715431538943</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.799953021861128</v>
+        <v>2.35766223252814</v>
       </c>
       <c r="E21" t="n">
-        <v>0.171064772012977</v>
+        <v>0.0630421270836352</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0110049407041009</v>
+        <v>0.0311668363374638</v>
       </c>
     </row>
     <row r="22">
@@ -946,19 +937,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>3.21648403901593</v>
+        <v>3.11885578555424</v>
       </c>
       <c r="C22" t="n">
-        <v>0.324974101512846</v>
+        <v>0.257153849978277</v>
       </c>
       <c r="D22" t="n">
-        <v>3.06858557009487</v>
+        <v>2.42406676060331</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0532123255139728</v>
+        <v>0.0405027133359663</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0441016536718979</v>
+        <v>0.0206703711207999</v>
       </c>
     </row>
     <row r="23">
@@ -966,19 +957,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>1.35985235890837</v>
+        <v>0.147734736339588</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.336066569564482</v>
+        <v>-0.0614447180396839</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.15904759084562</v>
+        <v>-0.591245580395391</v>
       </c>
       <c r="E23" t="n">
-        <v>0.04463383199951</v>
+        <v>0.0791685602024474</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0388530760163527</v>
+        <v>0.00250453541131053</v>
       </c>
     </row>
     <row r="24">
@@ -986,19 +977,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>-4.77585579013447</v>
+        <v>0.709677995893539</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0407542506603729</v>
+        <v>0.234061812763669</v>
       </c>
       <c r="D24" t="n">
-        <v>0.389960753540153</v>
+        <v>2.25873967177553</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0779900841321501</v>
+        <v>0.0844636091724283</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00107192488401761</v>
+        <v>0.0392233909938528</v>
       </c>
     </row>
     <row r="25">
@@ -1006,79 +997,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>0.302361818813422</v>
+        <v>0.574718511087689</v>
       </c>
       <c r="C25" t="n">
-        <v>0.247569254003195</v>
+        <v>-0.463459665183608</v>
       </c>
       <c r="D25" t="n">
-        <v>2.34156231843771</v>
+        <v>-4.62320213127677</v>
       </c>
       <c r="E25" t="n">
-        <v>0.0563443513707369</v>
+        <v>0.143189132849986</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0272814239790748</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" t="n">
-        <v>3.09990777382625</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0.280291583537634</v>
-      </c>
-      <c r="D26" t="n">
-        <v>2.62129107939092</v>
-      </c>
-      <c r="E26" t="n">
-        <v>0.0347913966566757</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0206395361134537</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0.695762194658104</v>
-      </c>
-      <c r="C27" t="n">
-        <v>0.231247686773319</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2.21233268186614</v>
-      </c>
-      <c r="E27" t="n">
-        <v>0.0776717875718957</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.0343476818214027</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0.492276868895541</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.404908015023845</v>
-      </c>
-      <c r="D28" t="n">
-        <v>-3.96920230798655</v>
-      </c>
-      <c r="E28" t="n">
-        <v>0.121507929509856</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.181590029489928</v>
+        <v>0.297666259542319</v>
       </c>
     </row>
   </sheetData>
@@ -1094,408 +1025,393 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" t="s">
         <v>33</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>34</v>
-      </c>
-      <c r="C1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" t="s">
-        <v>36</v>
-      </c>
-      <c r="E1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>0.296296296296296</v>
+        <v>0.291666666666667</v>
       </c>
       <c r="D2" t="n">
         <v>127</v>
       </c>
       <c r="E2" t="n">
-        <v>0.329015544041451</v>
+        <v>0.356741573033708</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B3" t="n">
         <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>0.296296296296296</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="D3" t="n">
         <v>14</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0362694300518135</v>
+        <v>0.0393258426966292</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>0.185185185185185</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="D4" t="n">
         <v>98</v>
       </c>
       <c r="E4" t="n">
-        <v>0.253886010362694</v>
+        <v>0.275280898876405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
       </c>
       <c r="C5" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D5" t="n">
         <v>117</v>
       </c>
       <c r="E5" t="n">
-        <v>0.303108808290155</v>
+        <v>0.328651685393258</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6"/>
+      <c r="A6" t="s">
+        <v>39</v>
+      </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>0.185185185185185</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.077720207253886</v>
+        <v>0.0308988764044944</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0103626943005181</v>
+        <v>0.00280898876404494</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00259067357512953</v>
+        <v>0.0308988764044944</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B9" t="n">
         <v>1</v>
       </c>
       <c r="C9" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0308988764044944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>0.037037037037037</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0308988764044944</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>0.222222222222222</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0308988764044944</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>0.037037037037037</v>
+        <v>0.166666666666667</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0112359550561798</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>0.185185185185185</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0129533678756477</v>
+        <v>0.0112359550561798</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B14" t="n">
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D14" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0103626943005181</v>
+        <v>0.0308988764044944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B15" t="n">
         <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0308988764044944</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0740740740740741</v>
+        <v>0.125</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00518134715025907</v>
+        <v>0.0168539325842697</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B17" t="n">
         <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0284974093264249</v>
+        <v>0.0112359550561798</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.111111111111111</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0155440414507772</v>
+        <v>0.0280898876404494</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0155440414507772</v>
+        <v>0.00842696629213483</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0.037037037037037</v>
+        <v>0.0416666666666667</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0129533678756477</v>
+        <v>0.0196629213483146</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
-        <v>0.037037037037037</v>
+        <v>0.208333333333333</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>119</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0207253886010363</v>
+        <v>0.334269662921348</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>0.259259259259259</v>
+        <v>0.333333333333333</v>
       </c>
       <c r="D22" t="n">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="E22" t="n">
-        <v>0.339378238341969</v>
+        <v>0.303370786516854</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C23" t="n">
-        <v>0.259259259259259</v>
+        <v>0.458333333333333</v>
       </c>
       <c r="D23" t="n">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="E23" t="n">
-        <v>0.284974093264249</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24" t="n">
-        <v>13</v>
-      </c>
-      <c r="C24" t="n">
-        <v>0.481481481481481</v>
-      </c>
-      <c r="D24" t="n">
-        <v>145</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.375647668393782</v>
+        <v>0.362359550561798</v>
       </c>
     </row>
   </sheetData>
